--- a/data/trans_orig/P57B6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023</t>
+          <t>Población según se ha sentido tranquilo/a y relajado/a en 2023 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140489</t>
+          <t>140536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>182423</t>
+          <t>180098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>157850</t>
+          <t>155049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195336</t>
+          <t>194609</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310179</t>
+          <t>307278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362596</t>
+          <t>362954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225638</t>
+          <t>224779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>267896</t>
+          <t>265865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308799</t>
+          <t>308560</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>348953</t>
+          <t>350335</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>544739</t>
+          <t>544401</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>603797</t>
+          <t>604123</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,9%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74469</t>
+          <t>74236</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104009</t>
+          <t>104606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>193144</t>
+          <t>193590</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>235176</t>
+          <t>233996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275732</t>
+          <t>272725</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>326332</t>
+          <t>323545</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25952</t>
+          <t>26688</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24979</t>
+          <t>25293</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41409</t>
+          <t>40915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39912</t>
+          <t>39934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62306</t>
+          <t>60770</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>989504</t>
+          <t>989864</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1485766</t>
+          <t>1492544</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>467716</t>
+          <t>481027</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>756622</t>
+          <t>761567</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1576649</t>
+          <t>1562258</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2275720</t>
+          <t>2233891</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>591854</t>
+          <t>582379</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>962449</t>
+          <t>962007</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>992177</t>
+          <t>986697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1461988</t>
+          <t>1436572</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1693686</t>
+          <t>1701306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2326643</t>
+          <t>2388607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>180298</t>
+          <t>178163</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>303253</t>
+          <t>304314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261795</t>
+          <t>263952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>421765</t>
+          <t>421029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>497061</t>
+          <t>506826</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>699588</t>
+          <t>706169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>24325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50923</t>
+          <t>52896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46552</t>
+          <t>46330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81932</t>
+          <t>83765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77536</t>
+          <t>78110</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>123445</t>
+          <t>124665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259192</t>
+          <t>259771</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318466</t>
+          <t>318783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212430</t>
+          <t>212352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255303</t>
+          <t>254324</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484473</t>
+          <t>485036</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556522</t>
+          <t>562293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,02%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>225528</t>
+          <t>225495</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>281422</t>
+          <t>281472</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>264131</t>
+          <t>262413</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>309448</t>
+          <t>307947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>505278</t>
+          <t>503965</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>575147</t>
+          <t>573543</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69741</t>
+          <t>69062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104507</t>
+          <t>103820</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>109034</t>
+          <t>108907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142376</t>
+          <t>144539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>188006</t>
+          <t>185977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>236343</t>
+          <t>237700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31336</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25317</t>
+          <t>25548</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49877</t>
+          <t>50573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1433222</t>
+          <t>1436402</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2021428</t>
+          <t>2035671</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>872541</t>
+          <t>862948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1163453</t>
+          <t>1163595</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2389076</t>
+          <t>2431163</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3108324</t>
+          <t>3219051</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1036648</t>
+          <t>1024722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1466632</t>
+          <t>1463054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1601774</t>
+          <t>1607079</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2070682</t>
+          <t>2118872</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2826892</t>
+          <t>2783256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3508290</t>
+          <t>3425832</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>48,36%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>328211</t>
+          <t>330102</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>485051</t>
+          <t>484370</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>582278</t>
+          <t>577238</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>768988</t>
+          <t>768496</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>987893</t>
+          <t>983149</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1226067</t>
+          <t>1223441</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53556</t>
+          <t>51648</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94149</t>
+          <t>92609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>91062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137052</t>
+          <t>133219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155177</t>
+          <t>156859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216990</t>
+          <t>216344</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B6_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B6_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>160496</t>
+          <t>181542</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>140536</t>
+          <t>161014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>180098</t>
+          <t>202949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>175977</t>
+          <t>191914</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>155049</t>
+          <t>172327</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194609</t>
+          <t>211438</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>336473</t>
+          <t>373455</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>307278</t>
+          <t>347058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362954</t>
+          <t>401923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>245486</t>
+          <t>278080</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224779</t>
+          <t>254781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>265865</t>
+          <t>302552</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>329728</t>
+          <t>360523</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308560</t>
+          <t>337594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>350335</t>
+          <t>383288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>575215</t>
+          <t>638602</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>544401</t>
+          <t>607493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>604123</t>
+          <t>670342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88761</t>
+          <t>97422</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74236</t>
+          <t>81215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>104606</t>
+          <t>116305</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>210965</t>
+          <t>226699</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>193590</t>
+          <t>207448</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>233996</t>
+          <t>247714</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>299726</t>
+          <t>324121</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>272725</t>
+          <t>297192</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>323545</t>
+          <t>349292</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10935</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32390</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25293</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40915</t>
+          <t>45189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49772</t>
+          <t>54389</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39934</t>
+          <t>42900</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60770</t>
+          <t>67429</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>512126</t>
+          <t>575445</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>512126</t>
+          <t>575445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512126</t>
+          <t>575445</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749060</t>
+          <t>815123</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>749060</t>
+          <t>815123</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>749060</t>
+          <t>815123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1261186</t>
+          <t>1390567</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1261186</t>
+          <t>1390567</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1261186</t>
+          <t>1390567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1147062</t>
+          <t>985041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>989864</t>
+          <t>931387</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1492544</t>
+          <t>1043460</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>664426</t>
+          <t>747068</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>481027</t>
+          <t>702609</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>761567</t>
+          <t>789439</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1811488</t>
+          <t>1732109</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1562258</t>
+          <t>1668127</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2233891</t>
+          <t>1801274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>842660</t>
+          <t>917806</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>582379</t>
+          <t>864445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>962007</t>
+          <t>974323</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1136662</t>
+          <t>936091</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>986697</t>
+          <t>885251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1436572</t>
+          <t>976997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1979323</t>
+          <t>1853897</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1701306</t>
+          <t>1786685</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2388607</t>
+          <t>1919542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>256397</t>
+          <t>280851</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178163</t>
+          <t>249184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304314</t>
+          <t>315332</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>367349</t>
+          <t>412319</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>263952</t>
+          <t>381555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>421029</t>
+          <t>444678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>623746</t>
+          <t>693170</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>506826</t>
+          <t>650153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>706169</t>
+          <t>746691</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>40135</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>28941</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52896</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64929</t>
+          <t>71213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46330</t>
+          <t>58247</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83765</t>
+          <t>88153</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>101567</t>
+          <t>111348</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78110</t>
+          <t>92771</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124665</t>
+          <t>132350</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2282756</t>
+          <t>2223833</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2282756</t>
+          <t>2223833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2282756</t>
+          <t>2223833</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2233367</t>
+          <t>2166691</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2233367</t>
+          <t>2166691</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2233367</t>
+          <t>2166691</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4516123</t>
+          <t>4390524</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4516123</t>
+          <t>4390524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4516123</t>
+          <t>4390524</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>288359</t>
+          <t>314128</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259771</t>
+          <t>284702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318783</t>
+          <t>345356</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>232839</t>
+          <t>257952</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>212352</t>
+          <t>235638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>254324</t>
+          <t>281884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>521197</t>
+          <t>572080</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>485036</t>
+          <t>536046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>562293</t>
+          <t>609869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>254061</t>
+          <t>282574</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>225495</t>
+          <t>253928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>281472</t>
+          <t>311097</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>285022</t>
+          <t>316720</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>262413</t>
+          <t>293127</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>307947</t>
+          <t>341077</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>539083</t>
+          <t>599294</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>503965</t>
+          <t>563707</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>573543</t>
+          <t>636072</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>85881</t>
+          <t>95870</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69062</t>
+          <t>79315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103820</t>
+          <t>117485</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>125692</t>
+          <t>140015</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108907</t>
+          <t>121651</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144539</t>
+          <t>160054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>235885</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185977</t>
+          <t>211007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>237700</t>
+          <t>266722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>31742</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16911</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>29121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>39205</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>26723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50573</t>
+          <t>54716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1595917</t>
+          <t>1480711</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1436402</t>
+          <t>1417024</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2035671</t>
+          <t>1548012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1073242</t>
+          <t>1196934</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>862948</t>
+          <t>1139650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1163595</t>
+          <t>1251189</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2669159</t>
+          <t>2677645</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2431163</t>
+          <t>2596999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3219051</t>
+          <t>2763518</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>38,24%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1342208</t>
+          <t>1478459</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1024722</t>
+          <t>1410675</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1463054</t>
+          <t>1543038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1751413</t>
+          <t>1613334</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1607079</t>
+          <t>1556173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2118872</t>
+          <t>1668672</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3093620</t>
+          <t>3091793</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2783256</t>
+          <t>3010516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3425832</t>
+          <t>3170221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>431038</t>
+          <t>474144</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>330102</t>
+          <t>433922</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>484370</t>
+          <t>516632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>704005</t>
+          <t>779033</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>577238</t>
+          <t>738590</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>768496</t>
+          <t>822732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1135044</t>
+          <t>1253176</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>983149</t>
+          <t>1191844</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1223441</t>
+          <t>1308803</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,11%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>77551</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>51648</t>
+          <t>60436</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>92609</t>
+          <t>98027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>127390</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91062</t>
+          <t>109552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>148309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>186572</t>
+          <t>204942</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156859</t>
+          <t>178941</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216344</t>
+          <t>232071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3441505</t>
+          <t>3510865</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3441505</t>
+          <t>3510865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3441505</t>
+          <t>3510865</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3642890</t>
+          <t>3716691</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3642890</t>
+          <t>3716691</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3642890</t>
+          <t>3716691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7084395</t>
+          <t>7227556</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7084395</t>
+          <t>7227556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7084395</t>
+          <t>7227556</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
